--- a/estimate_template.xlsx
+++ b/estimate_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leon/Documents/研究室/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319CA07B-3B15-5A49-983E-E6126B3EE07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B861AC17-8DDF-F04D-A2D6-C76E64B0530F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{785139EF-8D00-FF4B-85E1-59D800A03D9B}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="27740" windowHeight="17380" xr2:uid="{785139EF-8D00-FF4B-85E1-59D800A03D9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -140,6 +140,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="42" formatCode="_ &quot;¥&quot;* #,##0_ ;_ &quot;¥&quot;* \-#,##0_ ;_ &quot;¥&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="12"/>
@@ -194,7 +197,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -209,6 +212,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -528,6 +537,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="8" max="9" width="10.7109375" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -537,16 +547,27 @@
       <c r="D1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="H1"/>
+      <c r="I1"/>
     </row>
     <row r="2" spans="1:10">
       <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="E2" s="5"/>
+      <c r="H2"/>
+      <c r="I2"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
+      <c r="H3"/>
+      <c r="I3"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="H4"/>
+      <c r="I4"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="3" t="s">
